--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N86_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N86_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>25.11842577567633</v>
+        <v>4.081744188547404</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98756124083962</v>
+        <v>3.897978701636438</v>
       </c>
       <c r="E2" t="n">
-        <v>8.620123401419566</v>
+        <v>1.400770052730679</v>
       </c>
       <c r="F2" t="n">
-        <v>8.705109052263193</v>
+        <v>1.414580220992769</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.00050256672357</v>
+        <v>5.20008166709258</v>
       </c>
       <c r="D3" t="n">
-        <v>30.8614005287745</v>
+        <v>5.014977585925856</v>
       </c>
       <c r="E3" t="n">
-        <v>8.620123401419566</v>
+        <v>1.400770052730679</v>
       </c>
       <c r="F3" t="n">
-        <v>8.705109052263193</v>
+        <v>1.414580220992769</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.58885908408806</v>
+        <v>6.59568960116431</v>
       </c>
       <c r="D4" t="n">
-        <v>39.91865263642166</v>
+        <v>6.48678105341852</v>
       </c>
       <c r="E4" t="n">
-        <v>8.620123401419566</v>
+        <v>1.400770052730679</v>
       </c>
       <c r="F4" t="n">
-        <v>8.705109052263193</v>
+        <v>1.414580220992769</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.61526311827423</v>
+        <v>5.787480256719562</v>
       </c>
       <c r="D5" t="n">
-        <v>34.24833617259991</v>
+        <v>5.565354628047486</v>
       </c>
       <c r="E5" t="n">
-        <v>8.620123401419566</v>
+        <v>1.400770052730679</v>
       </c>
       <c r="F5" t="n">
-        <v>8.705109052263193</v>
+        <v>1.414580220992769</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.85142976076649</v>
+        <v>2.575857336124554</v>
       </c>
       <c r="D6" t="n">
-        <v>14.72198126322075</v>
+        <v>2.392321955273372</v>
       </c>
       <c r="E6" t="n">
-        <v>8.620123401419566</v>
+        <v>1.400770052730679</v>
       </c>
       <c r="F6" t="n">
-        <v>8.705109052263193</v>
+        <v>1.414580220992769</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
